--- a/data_extactor/batch_10_fa/batch_0092_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0092_fa.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | مانیتورینگ | سخن گفتن</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | سخن گفتن</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -518,17 +518,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | ثبات دست و بازو | چالاکی دست | بینایی دور | زمان عکس‌العمل | هماهنگی چند عضو | دقت کنترل | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | درک کتبی | درک شفاهی | کنترل نرخ | جهت‌گیری پاسخ | چالاکی انگشتان | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | قدرت تنه | قدرت ایستا | وضوح گفتار | تشخیص رنگ بصری</t>
+          <t>بینایی نزدیک | ثبات دست و بازو | مهارت دستی | بینایی دور | زمان عکس‌العمل | هماهنگی چند عضو | دقت کنترل | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | درک کتبی | درک شفاهی | کنترل نرخ | جهت‌گیری پاسخ | مهارت انگشتان | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | قدرت تنه | قدرت ایستا | وضوح گفتار | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان به صورت ایستاده | فشار زمانی | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض آلاینده‌ها | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارگران | قرار گرفتن در معرض شرایط خطرناک | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | فراوانی تصمیم‌گیری | پیامدهای کاری و نتایج سایر کارگران | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | اهمیت تکرار وظایف یکسان | قرار گرفتن در معرض صداها، سطوح نویزی که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | سرعت تعیین‌شده توسط سرعت تجهیزات | تاثیر تصمیمات بر همکاران یا نتایج شرکت | ارتباط با دیگران | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض تجهیزات خطرناک | پیامد خطا | آزادی در تصمیم‌گیری | داخل ساختمان، محیط کنترل‌شده | صرف زمان برای خم کردن یا چرخاندن بدن</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای ایستادن | فشار زمانی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض آلاینده‌ها | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض شرایط خطرناک | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | فراوانی تصمیم‌گیری | پیامدهای کاری و نتایج سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | اهمیت تکرار وظایف یکسان | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | سرعت تعیین‌شده توسط سرعت تجهیزات | تأثیر تصمیمات بر همکاران یا نتایج شرکت | ارتباط با دیگران | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض تجهیزات خطرناک | پیامد خطا | آزادی در تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای خم کردن یا چرخاندن بدن</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | اپراتورها و متصدیان تجهیزات شیمیایی | اپراتورها و متصدیان تجهیزات تمیزکاری، شستشو و اسیدشویی فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های خردکن، سنگ‌زنی و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن و شکل‌دهی، الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | دسته‌ای‌سازان مواد غذایی | اپراتورها و متصدیان ماشین‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | اپراتورها و متصدیان کوره، کوره پخت، فر، خشک‌کن و دیگ بخار | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، پرداخت و بافینگ، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی، فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های آبکاری، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جداسازی، فیلتراسیون، شفاف‌سازی، رسوب‌دهی و تقطیر | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی منسوجات</t>
+          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | متصدیان و اپراتورهای تجهیزات شیمیایی | اپراتورها و متصدیان تجهیزات تمیزکاری، شستشو و اسیدشویی فلزات | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | بچ‌سازان مواد غذایی | اپراتورها و متصدیان ماشین‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | اپراتورها و متصدیان کوره، کوره پخت، فر، خشک‌کن و دیگ بخار | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی، فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های آبکاری، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاستیک | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، زلال‌سازی، ته‌نشینی و تقطیر | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی منسوجات</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>مانیتورینگ | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن | ریاضیات</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن | ریاضیات</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -575,17 +575,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>چالاکی دست | بینایی نزدیک | ثبات دست و بازو | ترتیب‌دهی اطلاعات | تشخیص گفتار | قدرت ایستا | دقت کنترل | انعطاف‌پذیری دسته‌بندی | درک شفاهی</t>
+          <t>مهارت دستی | بینایی نزدیک | ثبات دست و بازو | ترتیب‌دهی اطلاعات | تشخیص گفتار | قدرت ایستا | دقت کنترل | انعطاف‌پذیری دسته‌بندی | درک شفاهی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | داخل ساختمان، محیط کنترل‌شده | اهمیت دقیق یا درست بودن | صرف زمان به صورت ایستاده | صرف زمان برای انجام حرکات تکراری | فشار زمانی</t>
+          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | صرف زمان برای ایستادن | صرف زمان برای انجام حرکات تکراری | فشار زمانی</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس، فلز و پلاست | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | قالب‌سازان و هسته‌سازان ریخته‌گری | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، پرداخت و بافینگ، فلز و پلاست | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزار تراش و تراشکاری، فلز و پلاست | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فرز و صفحه‌تراش، فلز و پلاست | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاست | بسته‌بندها و بسته‌بندی‌کنندگان دستی | کارگران نقاشی، پوشش‌دهی و تزیین | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های کالاهای کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اره‌کاری، چوب | اپراتورهای ماشین دوخت | اپراتورها و متصدیان ماشین‌های کفش | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش منسوجات | تیزکنندگان و فیلرکنندگان ابزار | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌کاری، به جز اره‌کاری</t>
+          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | قالب‌سازان و ماهیچه‌سازان کارگاه ریخته‌گری | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | بسته‌بندهای دستی | کارگران نقاشی، پوشش‌دهی و تزیین | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تولید محصولات کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اره‌کشی چوب | اپراتورهای چرخ خیاطی | اپراتورها و متصدیان ماشین‌آلات کفش‌سازی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین برش منسوجات | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>مانیتورینگ | درک مطلب | تفکر انتقادی</t>
+          <t>نظارت | درک مطلب | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -632,17 +632,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>چالاکی انگشتان | دقت کنترل | بینایی نزدیک | ثبات دست و بازو | حساسیت به مسئله | چالاکی دست | تجسم فضایی | درک شفاهی | زمان عکس‌العمل | هماهنگی چند عضو | کنترل نرخ | استدلال قیاسی | ترتیب‌دهی اطلاعات | توجه انتخابی | درک عمق | انعطاف‌پذیری گسترده | قدرت تنه | قدرت ایستا | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | درک کتبی | جهت‌گیری پاسخ | استدلال استقرایی | بیان شفاهی</t>
+          <t>مهارت انگشتان | دقت کنترل | بینایی نزدیک | ثبات دست و بازو | حساسیت به مسئله | مهارت دستی | تجسم | درک شفاهی | زمان عکس‌العمل | هماهنگی چند عضو | کنترل نرخ | استدلال قیاسی | ترتیب‌دهی اطلاعات | توجه انتخابی | درک عمق | انعطاف‌پذیری دامنه حرکت | قدرت تنه | قدرت ایستا | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | درک کتبی | جهت‌گیری پاسخ | استدلال استقرایی | بیان شفاهی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان به صورت ایستاده | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض صداها، سطوح نویزی که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض تجهیزات خطرناک | صرف زمان برای انجام حرکات تکراری | سلامت و ایمنی سایر کارگران | تاثیر تصمیمات بر همکاران یا نتایج شرکت | سرعت تعیین‌شده توسط سرعت تجهیزات | فشار زمانی | اهمیت تکرار وظایف یکسان | صرف زمان برای پیاده‌روی یا دویدن | قرار گرفتن در معرض آلاینده‌ها | ارتباط با دیگران | فراوانی تصمیم‌گیری | پیامدهای کاری و نتایج سایر کارگران | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | صرف زمان برای خم کردن یا چرخاندن بدن</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای ایستادن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض تجهیزات خطرناک | صرف زمان برای انجام حرکات تکراری | سلامت و ایمنی سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | سرعت تعیین‌شده توسط سرعت تجهیزات | فشار زمانی | اهمیت تکرار وظایف یکسان | صرف زمان برای راه رفتن یا دویدن | قرار گرفتن در معرض آلاینده‌ها | ارتباط با دیگران | فراوانی تصمیم‌گیری | پیامدهای کاری و نتایج سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | صرف زمان برای خم کردن یا چرخاندن بدن</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های خردکن، سنگ‌زنی و پرداخت | برش‌دهندگان و پرداخت‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس، فلز و پلاست | تنظیم‌کنندگان, اپراتورها و متصدیان ماشین‌های اکستروژن و شکل‌دهی، الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، پرداخت و بافینگ، فلز و پلاست | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزار تراش و تراشکاری، فلز و پلاست | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فرز و صفحه‌تراش، فلز و پلاست | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای چندگانه، فلز و پلاست | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های کالاهای کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاست | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اره‌کاری، چوب | اپراتورها و متصدیان ماشین‌های کفش | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش منسوجات | تیزکنندگان و فیلرکنندگان ابزار | ابزارسازان و قالب‌سازان | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌کاری، به جز اره‌کاری</t>
+          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | برش‌دهندگان و پرداخت‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تولید محصولات کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اره‌کشی چوب | اپراتورها و متصدیان ماشین‌آلات کفش‌سازی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین برش منسوجات | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | سازندگان ابزار و قالب | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,27 +679,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>مانیتورینگ | سخن گفتن | تفکر انتقادی | گوش دادن فعال | درک مطلب</t>
+          <t>نظارت | سخن گفتن | تفکر انتقادی | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | مکانیک | کامپیوتر و الکترونیک</t>
+          <t>تولید و فرآوری | مکانیک | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>سرعت ادراکی | کنترل نرخ | زمان عکس‌العمل | ثبات دست و بازو | بینایی نزدیک | چالاکی دست | حساسیت به مسئله | ترتیب‌دهی اطلاعات | چالاکی انگشتان | دقت کنترل | بینایی دور | توجه شنیداری | استقامت | قدرت تنه | قدرت ایستا | هماهنگی چند عضو | توجه انتخابی | تجسم فضایی | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | بیان شفاهی | درک کتبی | درک شفاهی | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | حساسیت شنوایی | درک عمق | جهت‌گیری پاسخ</t>
+          <t>سرعت ادراکی | کنترل نرخ | زمان عکس‌العمل | ثبات دست و بازو | بینایی نزدیک | مهارت دستی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | مهارت انگشتان | دقت کنترل | بینایی دور | توجه شنیداری | استقامت | قدرت تنه | قدرت ایستا | هماهنگی چند عضو | توجه انتخابی | تجسم | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | بیان شفاهی | درک کتبی | درک شفاهی | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | حساسیت شنوایی | درک عمق | جهت‌گیری پاسخ</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان به صورت ایستاده | قرار گرفتن در معرض صداها، سطوح نویزی که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | سرعت تعیین‌شده توسط سرعت تجهیزات | قرار گرفتن در معرض آلاینده‌ها | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای استفاده از دست‌ها جهت جابجایی, کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | ارتباط با دیگران | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | فشار زمانی | فراوانی تصمیم‌گیری | اهمیت تکرار وظایف یکسان | نزدیکی فیزیکی | قرار گرفتن در معرض سوختگی‌های جزئی، برش‌ها، گازگرفتگی‌ها یا نیش‌ها | تاثیر تصمیمات بر همکاران یا نتایج شرکت | سلامت و ایمنی سایر کارگران | صرف زمان برای پیاده‌روی یا دویدن | آزادی در تصمیم‌گیری | قرار گرفتن در معرض تجهیزات خطرناک</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای ایستادن | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سرعت تعیین‌شده توسط سرعت تجهیزات | قرار گرفتن در معرض آلاینده‌ها | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | ارتباط با دیگران | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | فشار زمانی | فراوانی تصمیم‌گیری | اهمیت تکرار وظایف یکسان | نزدیکی فیزیکی | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | سلامت و ایمنی سایر کارکنان | صرف زمان برای راه رفتن یا دویدن | آزادی در تصمیم‌گیری | قرار گرفتن در معرض تجهیزات خطرناک</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های خردکن، سنگ‌زنی و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس، فلز و پلاست | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن و کشش، فلز و پلاست | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن و شکل‌دهی، الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های آهنگری، فلز و پلاست | اپراتورها و متصدیان کوره، کوره پخت، فر، خشک‌کن و دیگ بخار | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، پرداخت و بافینگ، فلز و پلاست | مکانیک‌های ماشین‌آلات صنعتی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فرز و صفحه‌تراش، فلز و پلاست | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاست | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های قالب‌سازی، هسته‌سازی و ریخته‌گری، فلز و پلاست | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های کالاهای کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاست | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جداسازی، فیلتراسیون، شفاف‌سازی، رسوب‌دهی و تقطیر | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌کاری، به جز اره‌کاری</t>
+          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود و کشش، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فورج، فلز و پلاستیک | اپراتورها و متصدیان کوره، کوره پخت، فر، خشک‌کن و دیگ بخار | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاست | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تولید محصولات کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاستیک | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، زلال‌سازی، ته‌نشینی و تقطیر | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی | مانیتورینگ</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -746,17 +746,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | دقت کنترل | درک کتب | درک شفاهی | تشخیص گفتار | ثبات دست و بازو | بینایی نزدیک | وضوح گفتار | زمان عکس‌العمل | توجه انتخابی | ترتیب‌دهی اطلاعات | بیان شفاهی | استدلال استقرایی | استدلال قیاسی | چالاکی دست | سرعت ادراکی | قدرت تنه | هماهنگی چند عضو</t>
+          <t>حساسیت به مسئله | دقت کنترل | درک کتبی | درک شفاهی | تشخیص گفتار | ثبات دست و بازو | بینایی نزدیک | وضوح گفتار | زمان عکس‌العمل | توجه انتخابی | ترتیب‌دهی اطلاعات | بیان شفاهی | استدلال استقرایی | استدلال قیاسی | مهارت دستی | سرعت ادراکی | قدرت تنه | هماهنگی چند عضو</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض صداها، سطوح نویزی که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض آلاینده‌ها | سلامت و ایمنی سایر کارگران | داخل ساختمان، بدون کنترل محیطی | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض سوختگی‌های جزئی، برش‌ها، گازگرفتگی‌ها یا نیش‌ها | پیامد خطا | پیامدهای کاری و نتایج سایر کارگران | اهمیت دقیق یا درست بودن | تاثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان به صورت ایستاده | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | قرار گرفتن در معرض تجهیزات خطرناک | سرعت تعیین‌شده توسط سرعت تجهیزات | آزادی در تصمیم‌گیری | صرف زمان برای انجام حرکات تکراری</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض آلاینده‌ها | سلامت و ایمنی سایر کارکنان | محیط داخلی، بدون کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | پیامد خطا | پیامدهای کاری و نتایج سایر کارکنان | اهمیت دقیق یا درست بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای ایستادن | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | قرار گرفتن در معرض تجهیزات خطرناک | سرعت تعیین‌شده توسط سرعت تجهیزات | آزادی در تصمیم‌گیری | صرف زمان برای انجام حرکات تکراری</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | اپراتورها و متصدیان تجهیزات شیمیایی | اپراتورهای سیستم و پالایشگاه شیمیایی | اپراتورها و متصدیان تجهیزات تمیزکاری، شستشو و اسیدشویی فلزات | اپراتورها و متصدیان تجهیزات سرمایشی و انجماد | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های خردکن، سنگ‌زنی و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن و شکل‌دهی، الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | اپراتورها و متصدیان ماشین‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، پرداخت و بافینگ، فلز و پلاست | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی، فلز و پلاست | مکانیک‌های ماشین‌آلات صنعتی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین | کارگران تعمیر و نگهداری، ماشین‌آلات | اپراتورها و متصدیان کوره تصفیه فلز | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های مخلوط‌کن و ترکیب‌کننده | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاست | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جداسازی، فیلتراسیون، شفاف‌سازی، رسوب‌دهی و تقطیر | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی منسوجات</t>
+          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | متصدیان و اپراتورهای تجهیزات شیمیایی | اپراتورهای کارخانه و سامانه‌های شیمیایی | اپراتورها و متصدیان تجهیزات تمیزکاری، شستشو و اسیدشویی فلزات | اپراتورها و متصدیان تجهیزات سرمایشی و انجماد | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | اپراتورها و متصدیان ماشین‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی، فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | اپراتورها و متصدیان کوره تصفیه فلز | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های مخلوط‌کن و ترکیب‌کننده | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاستیک | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، زلال‌سازی، ته‌نشینی و تقطیر | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی منسوجات</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -788,32 +788,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Apache Hive | Apache Pig | Atlassian JIRA | Autodesk AutoCAD | نرم‌افزار طراحی به کمک کامپیوتر | نرم‌افزار بازرسی به کمک کامپیوتر | نرم‌افزار ماشین اندازه‌گیری مختصات | Cybermetrics GAGETrak | Dassault Systemes CATIA | Dassault Systemes SolidWorks | نرم‌افزار تحلیل داده | نرم‌افزار ورود داده | نرم‌افزار پایگاه داده | نرم‌افزار طراحی آزمایش‌ها DOE | زبان نشانه‌گذاری گسترش‌پذیر XML | FileMaker Pro | IBM Lotus Notes | IBM Notes | سیستم‌های علامت‌گذاری بازرسی | سیستم‌های بازرسی برچسب | Mastercam Design | نرم‌افزار طراحی و تولید به کمک کامپیوتر Mastercam | نرم‌افزار کدگذاری شرایط پزشکی | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Visio | Microsoft Word | Minitab | R | نرم‌افزار SAP | Selenium | Skype | دستگاه‌های جمع‌آوری داده کنترل فرآیند آماری SPC | زبان پرس‌وجوی ساختاریافته SQL | The MathWorks MATLAB | نرم‌افزار تحلیل تلرانس | Verisurf Metrology | Wilcox Associates PC-DMIS Inspection Planner</t>
+          <t>Apache Hive | Apache Pig | Atlassian JIRA | Autodesk AutoCAD | نرم‌افزار طراحی به کمک کامپیوتر | نرم‌افزار بازرسی به کمک کامپیوتر | نرم‌افزار ماشین اندازه‌گیری مختصات | Cybermetrics GAGETrak | Dassault Systemes CATIA | Dassault Systemes SolidWorks | نرم‌افزار تحلیل داده | نرم‌افزار ورود داده | نرم‌افزار پایگاه داده | نرم‌افزار طراحی آزمایش‌ها DOE | زبان نشانه‌گذاری توسعه‌پذیر XML | FileMaker Pro | IBM Lotus Notes | IBM Notes | سیستم‌های علامت‌گذاری بازرسی | سیستم‌های بازرسی برچسب | Mastercam Design | نرم‌افزار طراحی و تولید به کمک کامپیوتر Mastercam | نرم‌افزار کدگذاری شرایط پزشکی | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Visio | Microsoft Word | Minitab | R | نرم‌افزار SAP | Selenium | Skype | دستگاه‌های جمع‌آوری داده کنترل فرآیند آماری SPC | زبان پرس‌وجوی ساختاریافته SQL | The MathWorks MATLAB | نرم‌افزار تحلیل تلرانس | Verisurf Metrology | Wilcox Associates PC-DMIS Inspection Planner</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نگارش | سخن گفتن | درک مطلب | گوش دادن فعال | مانیتورینگ</t>
+          <t>تفکر انتقادی | نگارش | سخن گفتن | درک مطلب | گوش دادن فعال | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | زبان انگلیسی | خدمات مشتریان و پرسنلی | مکانیک | ریاضیات</t>
+          <t>تولید و فرآوری | زبان انگلیسی | خدمات مشتری و شخصی | مکانیک | ریاضیات</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>بیان شفاهی | بینایی نزدیک | درک شفاهی | سرعت ادراکی | حساسیت به مسئله | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | درک کتبی | وضوح گفتار | تشخیص گفتار | چالاکی انگشتان | چالاکی دست | ثبات دست و بازو | توجه انتخابی | تجسم فضایی | استدلال قیاسی</t>
+          <t>بیان شفاهی | بینایی نزدیک | درک شفاهی | سرعت ادراکی | حساسیت به مسئله | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | درک کتبی | وضوح گفتار | تشخیص گفتار | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | توجه انتخابی | تجسم | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | داخل ساختمان، بدون کنترل محیطی | قرار گرفتن در معرض آلاینده‌ها | ایمیل | قرار گرفتن در معرض صداها، سطوح نویزی که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | پیامدهای کاری و نتایج سایر کارگران | سلامت و ایمنی سایر کارگران | صرف زمان به صورت ایستاده | فراوانی تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | مکالمات تلفنی | فشار زمانی | تاثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت تکرار وظایف یکسان | صرف زمان برای پیاده‌روی یا دویدن</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، بدون کنترل شرایط محیطی | قرار گرفتن در معرض آلاینده‌ها | ایمیل | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامدهای کاری و نتایج سایر کارکنان | سلامت و ایمنی سایر کارکنان | صرف زمان برای ایستادن | فراوانی تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | مکالمات تلفنی | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت تکرار وظایف یکسان | صرف زمان برای راه رفتن یا دویدن</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | فناوران و تکنسین‌های کالیبراسیون | نصابان و تعمیرکنندگان کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکنندگان موتور الکتریکی، ابزار برقی و موارد مرتبط | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | مونتاژکنندگان تجهیزات الکترومکانیکی | مونتاژکنندگان موتور و سایر ماشین‌ها | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن و کشش، فلز و پلاست | مکانیک‌های ماشین‌آلات صنعتی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین | ماشین‌کاران | فناوران و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فرز و صفحه‌تراش، فلز و پلاست | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای چندگانه، فلز و پلاست | مونتاژکنندگان و تنظیم‌کنندگان دستگاه‌های زمان‌سنجی | توزین‌کنندگان، اندازه‌گیران، کنترل‌کنندگان و نمونه‌برداران، ثبت اسناد | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جوشکاری، لحیم‌کاری نرم و لحیم‌کاری سخت</t>
+          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود و کشش، فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | ماشین‌کاران | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکانیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار، فلز و پلاستیک | مونتاژکاران و تنظیم‌کنندگان دستگاه‌های زمان‌سنجی | توزین‌کنندگان، اندازه‌گیران، کنترل‌کنندگان و نمونه‌برداران، ثبت اسناد | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری نرم و لحیم‌کاری سخت</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -855,22 +855,22 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و پرسنلی | طراحی | تولید و فرآوری | فروش و بازاریابی | مدیریت و امور اداری | مکانیک | مهندسی و فناوری | ریاضیات | اداری | هنرهای زیبا | اقتصاد و حسابداری | آموزش و تربیت</t>
+          <t>خدمات مشتری و شخصی | طراحی | تولید و فرآوری | فروش و بازاریابی | مدیریت و اداره | مکانیک | مهندسی و فناوری | ریاضیات | اداری | هنرهای زیبا | اقتصاد و حسابداری | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | چالاکی انگشتان | ثبات دست و بازو | درک شفاهی | تجسم فضایی | انعطاف‌پذیری دسته‌بندی | اصالت | بیان شفاهی | تشخیص گفتار | تشخیص رنگ بصری | ترتیب‌دهی اطلاعات | استدلال قیاسی | حساسیت به مسئله | وضوح گفتار</t>
+          <t>بینایی نزدیک | مهارت انگشتان | ثبات دست و بازو | درک شفاهی | تجسم | انعطاف‌پذیری دسته‌بندی | اصالت | بیان شفاهی | تشخیص گفتار | تشخیص رنگ بصری | ترتیب‌دهی اطلاعات | استدلال قیاسی | حساسیت به مسئله | وضوح گفتار</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>داخل ساختمان، محیط کنترل‌شده | اهمیت دقیق یا درست بودن | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فراوانی تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | ارتباط با دیگران | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان به صورت نشسته | ایمیل | قرار گرفتن در معرض آلاینده‌ها | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | اهمیت تکرار وظایف یکسان | پیامدهای کاری و نتایج سایر کارگران</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | ارتباط با دیگران | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای نشستن | ایمیل | قرار گرفتن در معرض آلاینده‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | اهمیت تکرار وظایف یکسان | پیامدهای کاری و نتایج سایر کارکنان</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>کابینت‌سازان و نجاران کارگاهی | هنرمندان صنایع دستی | برش‌دهندگان و پرداخت‌کاران دستی | قلم‌زنان و حکاکان | پرداخت‌کاران مبلمان | کارگران گوهر و الماس | شیشه‌گران، قالب‌سازان، خم‌کنندگان و پرداخت‌کاران | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، پرداخت و بافینگ، فلز و پلاست | کارگران طرح‌بندی، فلز و پلاست | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاست | کارگران نقاشی، پوشش‌دهی و تزیین | الگو‌سازان، فلز و پلاست | الگوسازان، چوب | دوزندگان دستی | کارگران و تعمیرکنندگان کفش و چرم | سنگ‌تراشان و قلم‌زنان سنگ، تولیدی | سازندگان و مونتاژکنندگان سازه‌های فلزی | تیزکنندگان و فیلرکنندگان ابزار | ابزارسازان و قالب‌سازان</t>
+          <t>کابینت‌سازان و نجاران نیمکت | هنرمندان صنایع دستی | برش‌دهندگان و پرداخت‌کاران دستی | حکاکان و تیزاب‌کاران | پرداخت‌کاران مبلمان | کارگران گوهر و الماس | شیشه‌گران، قالب‌سازان، خم‌کاران و پرداخت‌کاران شیشه | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | کارگران شابلون‌زنی، فلز و پلاستیک | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | کارگران نقاشی، پوشش‌دهی و تزیین | الگوسازان فلز و پلاستیک | الگوسازان چوب | دوزندگان دستی | کارگران و تعمیرکاران کفش و چرم | سنگ‌تراشان و قلم‌زنان سنگ، تولیدی | سازندگان و مونتاژکاران فلزات سازه‌ای | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | سازندگان ابزار و قالب</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخن گفتن | مانیتورینگ | تفکر انتقادی</t>
+          <t>گوش دادن فعال | سخن گفتن | نظارت | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و پرسنلی | تولید و فرآوری | زبان انگلیسی | ریاضیات</t>
+          <t>خدمات مشتری و شخصی | تولید و فرآوری | زبان انگلیسی | ریاضیات</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | چالاکی انگشتان | ثبات دست و بازو | تشخیص رنگ بصری | حساسیت به مسئله | دقت کنترل | چالاکی دست | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | بیان شفاهی | درک شفاهی | وضوح گفتار | تشخیص گفتار | توجه انتخابی | تجسم فضایی | ترتیب‌دهی اطلاعات</t>
+          <t>بینایی نزدیک | مهارت انگشتان | ثبات دست و بازو | تشخیص رنگ بصری | حساسیت به مسئله | دقت کنترل | مهارت دستی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | بیان شفاهی | درک شفاهی | وضوح گفتار | تشخیص گفتار | توجه انتخابی | تجسم | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>داخل ساختمان, محیط کنترل‌شده | اهمیت دقیق یا درست بودن | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | صرف زمان به صورت نشسته | مکالمات تلفنی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت تکرار وظایف یکسان | نامه‌ها و یادداشت‌های مکتوب | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | تاثیر تصمیمات بر همکاران یا نتایج شرکت | کار با یا مشارکت در یک گروه کاری یا تیم | ایمیل | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای انجام حرکات تکراری | فشار زمانی</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | صرف زمان برای نشستن | مکالمات تلفنی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت تکرار وظایف یکسان | نامه‌ها و یادداشت‌های کتبی | تعامل با مشتریان خارجی یا عموم مردم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | کار با یا مشارکت در یک گروه کاری یا تیم | ایمیل | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای انجام حرکات تکراری | فشار زمانی</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>برش‌دهندگان و پرداخت‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | قلم‌زنان و حکاکان | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، پرداخت و بافینگ، فلز و پلاست | جواهرسازان و کارگران سنگ‌ها و فلزات قیمتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزار تراش و تراشکاری، فلز و پلاست | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فرز و صفحه‌تراش، فلز و پلاست | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاست | تکنسین‌های آزمایشگاه اپتیک | کارگران نقاشی، پوشش‌دهی و تزیین | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های آبکاری، فلز و پلاست | سنگ‌شکنان، معدن سنگ | اپراتورها و متصدیان ماشین‌های کفش | کارگران و تعمیرکنندگان کفش و چرم | سنگ‌تراشان و قلم‌زنان سنگ، تولیدی | مونتاژکنندگان و تنظیم‌کنندگان دستگاه‌های زمان‌سنجی | تیزکنندگان و فیلرکنندگان ابزار | ابزارسازان و قالب‌سازان | تعمیرکنندگان ساعت</t>
+          <t>برش‌دهندگان و پرداخت‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | حکاکان و تیزاب‌کاران | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | جواهرسازان و کارگران سنگ‌ها و فلزات قیمتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تراشکاری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | تکنسین‌های آزمایشگاه چشم‌پزشکی | کارگران نقاشی، پوشش‌دهی و تزیین | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های آبکاری، فلز و پلاستیک | سنگ‌شکنان معدن | اپراتورها و متصدیان ماشین‌آلات کفش‌سازی | کارگران و تعمیرکاران کفش و چرم | سنگ‌تراشان و قلم‌زنان سنگ، تولیدی | مونتاژکاران و تنظیم‌کنندگان دستگاه‌های زمان‌سنجی | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | سازندگان ابزار و قالب | تعمیرکاران ساعت مچی و دیواری</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -959,32 +959,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>نرم‌افزار حسابداری | نرم‌افزار طراحی و ترسیم به کمک کامپیوتر CADD | نرم‌افزار تصویربرداری کامپیوتری | نرم‌افزار مدیریت پایگاه داده | نرم‌افزار طراحی محصولات دندانپزشکی | نرم‌افزار تولید محصولات دندانپزشکی | Easy Solutions Easy Lab | نرم‌افزار ایمیل | نرم‌افزار گرافیکی | Intuit QuickBooks | Inventrix Labtrac | Jenmar International DL-Plus | LabMagic | Laboratory Systems Group Lab Manager | Mainstreet Systems &amp; Software DentaLab/PC II | Mainstreet Systems &amp; Software DentaRX | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | نرم‌افزار برنامه‌ریزی | نرم‌افزار مرورگر وب</t>
+          <t>نرم‌افزار حسابداری | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | نرم‌افزار تصویربرداری کامپیوتری | نرم‌افزار مدیریت پایگاه داده | نرم‌افزار طراحی محصولات دندانپزشکی | نرم‌افزار تولید محصولات دندانپزشکی | Easy Solutions Easy Lab | نرم‌افزار ایمیل | نرم‌افزار گرافیکی | Intuit QuickBooks | Inventrix Labtrac | Jenmar International DL-Plus | LabMagic | Laboratory Systems Group Lab Manager | Mainstreet Systems &amp; Software DentaLab/PC II | Mainstreet Systems &amp; Software DentaRX | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | نرم‌افزار زمان‌بندی | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | مانیتورینگ | یادگیری فعال | سخن گفتن | گوش دادن فعال</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | یادگیری فعال | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | طراحی | زبان انگلیسی | پزشکی و دندانپزشکی | تولید و فرآوری | آموزش و تربیت | خدمات مشتریان و پرسنلی | مکانیک | کامپیوتر و الکترونیک</t>
+          <t>مدیریت و اداره | طراحی | زبان انگلیسی | پزشکی و دندان‌پزشکی | تولید و فرآوری | آموزش و پرورش | خدمات مشتری و شخصی | مکانیک | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>چالاکی انگشتان | بینایی نزدیک | ثبات دست و بازو | دقت کنترل | تجسم فضایی | ترتیب‌دهی اطلاعات | استدلال قیاسی | حساسیت به مسئله | توجه انتخابی | چالاکی دست | درک کتبی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | درک شفاهی | سرعت ادراکی | انعطاف‌پذیری بستار | استدلال استقرایی | بیان شفاهی | تشخیص رنگ بصری</t>
+          <t>مهارت انگشتان | بینایی نزدیک | ثبات دست و بازو | دقت کنترل | تجسم | ترتیب‌دهی اطلاعات | استدلال قیاسی | حساسیت به مسئله | توجه انتخابی | مهارت دستی | درک کتبی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | درک شفاهی | سرعت ادراکی | انعطاف‌پذیری بستار | استدلال استقرایی | بیان شفاهی | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>فشار زمانی | اهمیت دقیق یا درست بودن | داخل ساختمان، محیط کنترل‌شده | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض آلاینده‌ها | صرف زمان به صورت نشسته | تعیین وظایف، اولویت‌ها و اهداف | استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | صرف زمان برای انجام حرکات تکراری | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت تکرار وظایف یکسان | تاثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض بیماری یا عفونت‌ها | قرار گرفتن در معرض سوختگی‌های جزئی، برش‌ها، گازگرفتگی‌ها یا نیش‌ها | پیامدهای کاری و نتایج سایر کارگران</t>
+          <t>فشار زمانی | اهمیت دقیق یا درست بودن | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای نشستن | تعیین وظایف، اولویت‌ها و اهداف | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | صرف زمان برای انجام حرکات تکراری | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت تکرار وظایف یکسان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | پیامدهای کاری و نتایج سایر کارکنان</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | فناوران و تکنسین‌های کالیبراسیون | دستیاران دندانپزشک | بهداشت‌کاران دهان و دندان | دندانپزشکان عمومی | تکنسین‌های آندوسکوپی | قلم‌زنان و حکاکان | پرداخت‌کاران مبلمان | کارگران سنگ‌زنی و پرداخت دستی | تکنسین‌های تجهیزات پزشکی | تعمیرکنندگان تجهیزات پزشکی | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاست | تکنسین‌های آزمایشگاه اپتیک | متخصصان ارتودنسی | متخصصان ارتز و پروتز | کارگران نقاشی، پوشش‌دهی و تزیین | متخصصان پروتزهای دندانی | سازندگان و مونتاژکنندگان سازه‌های فلزی | تکنسین‌های جراحی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جوشکاری، لحیم‌کاری نرم و لحیم‌کاری سخت</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | دستیاران دندان‌پزشکی | بهداشت‌کاران دهان و دندان | دندانپزشکان، عمومی | تکنسین‌های آندوسکوپی | حکاکان و تیزاب‌کاران | پرداخت‌کاران مبلمان | کارگران سنگ‌زنی و پرداخت دستی | تکنسین‌های تجهیزات پزشکی | تعمیرکاران تجهیزات پزشکی | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | تکنسین‌های آزمایشگاه چشم‌پزشکی | متخصصان ارتودنسی | متخصصان ارتوپدی فنی و پروتز | کارگران نقاشی، پوشش‌دهی و تزیین | متخصصان پروتز دندان | سازندگان و مونتاژکاران فلزات سازه‌ای | تکنولوژیست‌های جراحی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری نرم و لحیم‌کاری سخت</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1016,32 +1016,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Autodesk AutoCAD | نرم‌افزار Footmaxx Metascan | نرم‌افزار تحلیل گیت | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | سیستم Ohio Willow Wood OMEGA Tracer | نرم‌افزار ساخت ارتز | Seattle Systems Shapemaker | SoftSource CADview | Vorum Research Corporation CANFIT-PLUS</t>
+          <t>Autodesk AutoCAD | نرم‌افزار Footmaxx Metascan | نرم‌افزار تحلیل راه رفتن | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | Ohio Willow Wood OMEGA Tracer System | نرم‌افزار ساخت ارتز | Seattle Systems Shapemaker | SoftSource CADview | Vorum Research Corporation CANFIT-PLUS</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن | مانیتورینگ | یادگیری فعال | نگارش</t>
+          <t>گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | خدمات مشتریان و پرسنلی | زبان انگلیسی | مکانیک | طراحی | آموزش و تربیت | ریاضیات</t>
+          <t>تولید و فرآوری | خدمات مشتری و شخصی | زبان انگلیسی | مکانیک | طراحی | آموزش و پرورش | ریاضیات</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | بینایی نزدیک | بیان شفاهی | استدلال قیاسی | تجسم فضایی | ثبات دست و بازو | ترتیب‌دهی اطلاعات | چالاکی انگشتان | وضوح گفتار | تشخیص گفتار | چالاکی دست | استدلال استقرایی | هماهنگی چند عضو | دقت کنترل | درک کتبی | اصالت | بیان کتبی | تشخیص رنگ بصری | قدرت تنه | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | حساسیت شنوایی | درک عمق</t>
+          <t>درک شفاهی | حساسیت به مسئله | بینایی نزدیک | بیان شفاهی | استدلال قیاسی | تجسم | ثبات دست و بازو | ترتیب‌دهی اطلاعات | مهارت انگشتان | وضوح گفتار | تشخیص گفتار | مهارت دستی | استدلال استقرایی | هماهنگی چند عضو | دقت کنترل | درک کتبی | اصالت | بیان کتبی | تشخیص رنگ بصری | قدرت تنه | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | حساسیت شنوایی | درک عمق</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>داخل ساختمان، محیط کنترل‌شده | قرار گرفتن در معرض آلاینده‌ها | استفاده از تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | فشار زمانی | فراوانی تصمیم‌گیری | صرف زمان به صورت ایستاده | قرار گرفتن در معرض تجهیزات خطرناک | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | قرار گرفتن در معرض صداها، سطوح نویزی که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | تاثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | پیامدهای کاری و نتایج سایر کارگران | نزدیکی فیزیکی | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | ایمیل | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | سلامت و ایمنی سایر کارگران | صرف زمان برای انجام حرکات تکراری</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | قرار گرفتن در معرض آلاینده‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | فشار زمانی | فراوانی تصمیم‌گیری | صرف زمان برای ایستادن | قرار گرفتن در معرض تجهیزات خطرناک | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | پیامدهای کاری و نتایج سایر کارکنان | نزدیکی فیزیکی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | ایمیل | تعامل با مشتریان خارجی یا عموم مردم | سلامت و ایمنی سایر کارکنان | صرف زمان برای انجام حرکات تکراری</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | فناوران و تکنسین‌های کالیبراسیون | تکنسین‌های پروتز دندان | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | مونتاژکنندگان تجهیزات الکترومکانیکی | تکنسین‌های آندوسکوپی | فناوران و تکنسین‌های مهندسی مکانیک | آماده‌کنندگان تجهیزات پزشکی | تعمیرکنندگان تجهیزات پزشکی | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاست | تکنسین‌های آزمایشگاه اپتیک | جراحان ارتوپدی، به جز اطفال | متخصصان ارتز و پروتز | جراحان اطفال | دوزندگان دستی | اپراتورها و متصدیان ماشین‌های کفش | کارگران و تعمیرکنندگان کفش و چرم | سازندگان و مونتاژکنندگان سازه‌های فلزی | تکنسین‌های جراحی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جوشکاری، لحیم‌کاری نرم و لحیم‌کاری سخت</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | تکنسین‌های پروتز دندان | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | مونتاژکاران تجهیزات الکترومکانیکی | تکنسین‌های آندوسکوپی | تکنسین‌ها و کارشناسان مهندسی مکانیک | آماده‌سازان تجهیزات پزشکی | تعمیرکاران تجهیزات پزشکی | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | تکنسین‌های آزمایشگاه چشم‌پزشکی | جراحان ارتوپد، به‌جز کودکان | متخصصان ارتوپدی فنی و پروتز | جراحان کودکان | دوزندگان دستی | اپراتورها و متصدیان ماشین‌آلات کفش‌سازی | کارگران و تعمیرکاران کفش و چرم | سازندگان و مونتاژکاران فلزات سازه‌ای | تکنولوژیست‌های جراحی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری نرم و لحیم‌کاری سخت</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0092_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0092_fa.xlsx
@@ -513,12 +513,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>تولید و پردازش</t>
+          <t>تولید و فرآوری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>دید نزدیک | ثبات دست و بازو | چابکی دستی | دید دور | زمان واکنش | هماهنگی چند اندام | دقت کنترل حرکتی | توجه انتخابی | سرعت ادراک | انعطاف‌پذیری در طبقه‌بندی | مرتب‌سازی اطلاعات | حساسیت به مسئله | درک کتبی | درک شفاهی | کنترل نرخ حرکت | جهت‌گیری پاسخ | چابکی انگشتان | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | استحکام بالاتنه | قدرت ایستا | وضوح گفتار | تشخیص تمایز رنگ‌ها</t>
+          <t>بینایی نزدیک | ثبات دست و بازو | مهارت دستی | بینایی دور | زمان عکس‌العمل | هماهنگی چند عضو | دقت کنترل | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | درک کتبی | درک شفاهی | کنترل نرخ | جهت‌گیری پاسخ | مهارت انگشتان | استدلال استقرایی | استدلال قیاسی | بیان شفاهی | قدرت تنه | قدرت ایستا | وضوح گفتار | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان دستگاه‌های اتصال چسبی | اپراتورها و متصدیان تجهیزات فرایندهای شیمیایی | اپراتورها و متصدیان تجهیزات شست‌وشو، نظافت و اسیدشویی فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های خردایش، سنگ‌زنی و پولیش | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ور Bastه‌کنی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن و فرم‌دهی الیاف شیشه و مصنوعی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | بچ‌سازان مواد غذایی | اپراتورها و متصدیان دستگاه‌های برشته‌کاری، پخت و خشک‌کن مواد غذایی و تنباکو | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و پاتیل‌های صنعتی | پرداخت‌کاران و صیقل‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، پرداخت و پولیش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی فلز و پلاستیک | تغذیه‌کنندگان و متصدیان تخلیه ماشین‌آلات صنعتی | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران (به‌جز فلز و پلاستیک) | اپراتورها و متصدیان دستگاه‌های بسته‌بندی و پرکن | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های آبکاری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های نورد فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جداسازی، فیلتراسیون، شفاف‌سازی، ته‌نشینی و تقطیر | اپراتورها و متصدیان ماشین‌آلات رنگرزی و سفیدگری منسوجات</t>
+          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | اپراتورها و متصدیان ماشین‌آلات و راکتورهای شیمیایی | اپراتورها و متصدیان تجهیزات شست‌وشو، نظافت و چربی‌زدایی فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | تولیدکنندگان فرمولی و دسته‌ای مواد غذایی | اپراتورهای ماشین‌آلات برشته‌کاری، پخت و خشک‌کن مواد غذایی و توتون | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و پاتیل‌های صنعتی | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای تجهیزات عملیات حرارتی فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | تنظیم‌کاران و اپراتورهای دستگاه‌های آبکاری فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی نساجی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,27 +565,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن | ریاضیات</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن | ریاضیات</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>تولید و پردازش</t>
+          <t>تولید و فرآوری</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>چابکی دستی | دید نزدیک | ثبات دست و بازو | مرتب‌سازی اطلاعات | تشخیص گفتار | قدرت ایستا | دقت کنترل حرکتی | انعطاف‌پذیری در طبقه‌بندی | درک شفاهی</t>
+          <t>مهارت دستی | بینایی نزدیک | ثبات دست و بازو | ترتیب‌دهی اطلاعات | تشخیص گفتار | قدرت ایستا | دقت کنترل | انعطاف‌پذیری دسته‌بندی | درک شفاهی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>استفاده از ابزارهای دستی و کنترل فیزیکی تجهیزات | محیط سرپوشیده با تهویهٔ مطبوع | اهمیت بالای دقت در کار | ایستادن طولانی‌مدت | انجام حرکات تکراری | فشار زمانی</t>
+          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | صرف زمان برای ایستادن | صرف زمان برای انجام حرکات تکراری | فشار زمانی</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان دستگاه‌های اتصال چسبی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ور Bastه‌کنی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | قالب‌سازان و ماهیچه‌سازان ریخته‌گری | پرداخت‌کاران و صیقل‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، پرداخت و پولیش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و متصدیان تخلیه ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های فرزکاری و صفحه‌تراشی فلز و پلاستیک | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران (به‌جز فلز و پلاستیک) | کارگران بسته‌بندی دستی | کارگران رنگ‌آمیزی، پوشش‌دهی و تزیین | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تولید محصولات کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اره‌کشی چوب | چرخکاران و دوزندگان صنعتی | اپراتورها و متصدیان ماشین‌آلات کفاشی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش منسوجات | سنگ‌زن‌ها، سوهان‌کاران و تیزکنندگان ابزار | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات صنایع چوب (به‌جز اره‌کشی)</t>
+          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | قالب‌گیران و ماهیچه‌سازان ریخته‌گری | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | کارگران بسته‌بندی دستی | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | تنظیم‌کنندگان و اپراتورهای ماشین‌های تولید محصولات کاغذی | تنظیم‌کنندگان، متصدیان و اپراتورهای اره‌ چوب‌بری | چرخکاران صنعتی | اپراتورها و متصدیان ماشین‌آلات کفش | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های برش منسوجات | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -627,12 +627,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>تولید و پردازش | ریاضیات | مکانیک</t>
+          <t>تولید و فرآوری | ریاضیات | مکانیک</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>چابکی انگشتان | دقت کنترل حرکتی | دید نزدیک | ثبات دست و بازو | حساسیت به مسئله | چابکی دستی | تجسم فضایی | درک شفاهی | زمان واکنش | هماهنگی چند اندام | کنترل نرخ حرکت | استدلال قیاسی | مرتب‌سازی اطلاعات | توجه انتخابی | ادراک عمق | انعطاف‌پذیری بدنی | استحکام بالاتنه | قدرت ایستا | سرعت ادراک | انعطاف‌پذیری در طبقه‌بندی | درک کتبی | جهت‌گیری پاسخ | استدلال استقرایی | بیان شفاهی</t>
+          <t>مهارت انگشتان | دقت کنترل | بینایی نزدیک | ثبات دست و بازو | حساسیت به مسئله | مهارت دستی | تجسم | درک شفاهی | زمان عکس‌العمل | هماهنگی چند عضو | کنترل نرخ | استدلال قیاسی | ترتیب‌دهی اطلاعات | توجه انتخابی | درک عمق | انعطاف‌پذیری دامنه حرکت | قدرت تنه | قدرت ایستا | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | درک کتبی | جهت‌گیری پاسخ | استدلال استقرایی | بیان شفاهی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان دستگاه‌های اتصال چسبی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های خردایش، سنگ‌زنی و پولیش | برشکاران و پیرایشگران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن و فرم‌دهی الیاف شیشه و مصنوعی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | پرداخت‌کاران و صیقل‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، پرداخت و پولیش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و متصدیان تخلیه ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های فرزکاری و صفحه‌تراشی فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای چندکاره فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تولید محصولات کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های نورد فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اره‌کشی چوب | اپراتورها و متصدیان ماشین‌آلات کفاشی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش منسوجات | سنگ‌زن‌ها، سوهان‌کاران و تیزکنندگان ابزار | قالب‌سازان و ابزارسازان صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات صنایع چوب (به‌جز اره‌کشی)</t>
+          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | برشکاران و پیرایشگران دستی | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های تولید محصولات کاغذی | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | تنظیم‌کنندگان، متصدیان و اپراتورهای اره‌ چوب‌بری | اپراتورها و متصدیان ماشین‌آلات کفش | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های برش منسوجات | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | قالب‌سازان و ابزارسازان صنعتی | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,22 +674,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>نرم‌افزار پایگاه داده عملیاتی | نرم‌افزار زمان‌بندی تولید | نرم‌افزار SAP | Microsoft Excel | Microsoft Office | Microsoft Outlook | Microsoft Word</t>
+          <t>نرم‌افزار پایگاه داده عملیاتی | نرم‌افزار Microsoft Office | نرم‌افزار SAP | Microsoft Excel | Microsoft Office | Microsoft Outlook | نرم‌افزار SAP</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>نظارت | سخن گفتن | تفکر انتقادی | شنیدن فعال | درک مطلب</t>
+          <t>نظارت | سخن گفتن | تفکر انتقادی | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>تولید و پردازش | مکانیک | رایانه و الکترونیک</t>
+          <t>تولید و فرآوری | مکانیک | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>سرعت ادراک | کنترل نرخ حرکت | زمان واکنش | ثبات دست و بازو | دید نزدیک | چابکی دستی | حساسیت به مسئله | مرتب‌سازی اطلاعات | چابکی انگشتان | دقت کنترل حرکتی | دید دور | توجه شنیداری | استقامت بدنی | استحکام بالاتنه | قدرت ایستا | هماهنگی چند اندام | توجه انتخابی | تجسم فضایی | انعطاف‌پذیری در طبقه‌بندی | استدلال قیاسی | بیان شفاهی | درک کتبی | درک شفاهی | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | حساسیت شنوایی | ادراک عمق | جهت‌گیری پاسخ</t>
+          <t>سرعت ادراکی | کنترل نرخ | زمان عکس‌العمل | ثبات دست و بازو | بینایی نزدیک | مهارت دستی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | مهارت انگشتان | دقت کنترل | بینایی دور | توجه شنیداری | استقامت | قدرت تنه | قدرت ایستا | هماهنگی چند عضو | توجه انتخابی | تجسم | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | بیان شفاهی | درک کتبی | درک شفاهی | استدلال استقرایی | وضوح گفتار | تشخیص گفتار | حساسیت شنوایی | درک عمق | جهت‌گیری پاسخ</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان دستگاه‌های اتصال چسبی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های خردایش، سنگ‌زنی و پولیش | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن و فرم‌دهی الیاف شیشه و مصنوعی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های آهنگری فلز و پلاستیک | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و پاتیل‌های صنعتی | پرداخت‌کاران و صیقل‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، پرداخت و پولیش فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تغذیه‌کنندگان و متصدیان تخلیه ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های فرزکاری و صفحه‌تراشی فلز و پلاستیک | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران (به‌جز فلز و پلاستیک) | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | اپراتورها و متصدیان دستگاه‌های بسته‌بندی و پرکن | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تولید محصولات کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های نورد فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جداسازی، فیلتراسیون، شفاف‌سازی، ته‌نشینی و تقطیر | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات صنایع چوب (به‌جز اره‌کشی)</t>
+          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان و اپراتورهای ماشین‌های فورجینگ فلز و پلاستیک | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و پاتیل‌های صنعتی | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | تنظیم‌کاران و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | تنظیم‌کنندگان و اپراتورهای ماشین‌های تولید محصولات کاغذی | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن | تفکر انتقادی | نظارت</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>مکانیک | تولید و پردازش | ایمنی و امنیت عمومی</t>
+          <t>مکانیک | تولید و فرآوری | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | دقت کنترل حرکتی | درک کتبی | درک شفاهی | تشخیص گفتار | ثبات دست و بازو | دید نزدیک | وضوح گفتار | زمان واکنش | توجه انتخابی | مرتب‌سازی اطلاعات | بیان شفاهی | استدلال استقرایی | استدلال قیاسی | چابکی دستی | سرعت ادراک | استحکام بالاتنه | هماهنگی چند اندام</t>
+          <t>حساسیت به مسئله | دقت کنترل | درک کتبی | درک شفاهی | تشخیص گفتار | ثبات دست و بازو | بینایی نزدیک | وضوح گفتار | زمان عکس‌العمل | توجه انتخابی | ترتیب‌دهی اطلاعات | بیان شفاهی | استدلال استقرایی | استدلال قیاسی | مهارت دستی | سرعت ادراکی | قدرت تنه | هماهنگی چند عضو</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان دستگاه‌های اتصال چسبی | اپراتورها و متصدیان تجهیزات فرایندهای شیمیایی | اپراتورهای تأسیسات و سیستم‌های شیمیایی | اپراتورها و متصدیان تجهیزات شست‌وشو، نظافت و اسیدشویی فلزات | اپراتورها و متصدیان سیستم‌های سرمایشی و انجماد | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های خردایش، سنگ‌زنی و پولیش | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن و فرم‌دهی الیاف شیشه و مصنوعی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | اپراتورها و متصدیان دستگاه‌های برشته‌کاری، پخت و خشک‌کن مواد غذایی و تنباکو | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، پرداخت و پولیش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان تجهیزات عملیات حرارتی فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تغذیه‌کنندگان و متصدیان تخلیه ماشین‌آلات صنعتی | تعمیرکاران ماشین‌آلات و تجهیزات صنعتی | اپراتورها و متصدیان کوره‌های ذوب و تصفیه فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های مخلوط‌کن و ترکیب مواد | اپراتورها و متصدیان دستگاه‌های بسته‌بندی و پرکن | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های نورد فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جداسازی، فیلتراسیون، شفاف‌سازی، ته‌نشینی و تقطیر | اپراتورها و متصدیان ماشین‌آلات رنگرزی و سفیدگری منسوجات</t>
+          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | اپراتورها و متصدیان ماشین‌آلات و راکتورهای شیمیایی | اپراتورهای تأسیسات و سیستم‌های فرایندی صنایع شیمیایی | اپراتورها و متصدیان تجهیزات شست‌وشو، نظافت و چربی‌زدایی فلزات | اپراتورها و متصدیان تجهیزات سرمایشی و انجماد | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | اپراتورهای ماشین‌آلات برشته‌کاری، پخت و خشک‌کن مواد غذایی و توتون | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای تجهیزات عملیات حرارتی فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | اپراتورها و متصدیان کوره‌های تصفیه و ذوب فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های مخلوط‌کن و ترکیب مواد | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی نساجی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نگارش | سخن گفتن | درک مطلب | شنیدن فعال | نظارت</t>
+          <t>تفکر انتقادی | نگارش | سخن گفتن | درک مطلب | گوش دادن فعال | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>تولید و پردازش | زبان انگلیسی | خدمات مشتریان و خدمات فردی | مکانیک | ریاضیات</t>
+          <t>تولید و فرآوری | زبان انگلیسی | خدمات مشتری و شخصی | مکانیک | ریاضیات</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>بیان شفاهی | دید نزدیک | درک شفاهی | سرعت ادراک | حساسیت به مسئله | انعطاف‌پذیری بستن الگو | انعطاف‌پذیری در طبقه‌بندی | مرتب‌سازی اطلاعات | درک کتبی | وضوح گفتار | تشخیص گفتار | چابکی انگشتان | چابکی دستی | ثبات دست و بازو | توجه انتخابی | تجسم فضایی | استدلال قیاسی</t>
+          <t>بیان شفاهی | بینایی نزدیک | درک شفاهی | سرعت ادراکی | حساسیت به مسئله | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | درک کتبی | وضوح گفتار | تشخیص گفتار | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | توجه انتخابی | تجسم | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان دستگاه‌های اتصال چسبی | مونتاژکاران سازه، سطوح، اتصالات و سیستم‌های هواپیما | کارشناسان و تکنسین‌های کالیبراسیون | نصابان و تعمیرکاران شیرآلات و کنترل‌کننده‌های صنعتی (به‌جز درب‌های مکانیکی) | تعمیرکاران الکتروموتورها، ابزارهای برقی و تجهیزات وابسته | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | تعمیرکاران تجهیزات برقی و الکترونیکی تجاری و صنعتی | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن و کشش فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تغذیه‌کنندگان و متصدیان تخلیه ماشین‌آلات صنعتی | تراشکاران و ماشین‌کاران صنعتی | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های فرزکاری و صفحه‌تراشی فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای چندکاره فلز و پلاستیک | مونتاژکاران و تنظیم‌کنندگان تجهیزات زمان‌سنجی و ساعت | توزین‌گران، متصدیان سنجش، بررسی‌کنندگان و نمونه‌برداران ثبتی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری سخت و نرم</t>
+          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | تکنسین‌ها و کارشناسان فنی کالیبراسیون | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و کشش فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تراشکاران، فرزکاران و ماشین‌کاران قطعات دقیق | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک | مونتاژکاران و تنظیم‌کنندگان ادوات زمان‌سنجی | متصدیان توزین، سنجش، بازرسی و نمونه‌برداری ثبت اسناد | تنظیم‌کاران و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | طراحی | تولید و پردازش | فروش و بازاریابی | مدیریت و امور اداری | مکانیک | مهندسی و فناوری | ریاضیات | امور اداری و دفتری | هنرهای تجسمی | اقتصاد و حسابداری | آموزش و تدریس</t>
+          <t>خدمات مشتری و شخصی | طراحی | تولید و فرآوری | فروش و بازاریابی | مدیریت و اداره | مکانیک | مهندسی و فناوری | ریاضیات | اداری | هنرهای زیبا | اقتصاد و حسابداری | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>دید نزدیک | چابکی انگشتان | ثبات دست و بازو | درک شفاهی | تجسم فضایی | انعطاف‌پذیری در طبقه‌بندی | ابتکار و اصالت | بیان شفاهی | تشخیص گفتار | تشخیص تمایز رنگ‌ها | مرتب‌سازی اطلاعات | استدلال قیاسی | حساسیت به مسئله | وضوح گفتار</t>
+          <t>بینایی نزدیک | مهارت انگشتان | ثبات دست و بازو | درک شفاهی | تجسم | انعطاف‌پذیری دسته‌بندی | اصالت | بیان شفاهی | تشخیص گفتار | تشخیص رنگ بصری | ترتیب‌دهی اطلاعات | استدلال قیاسی | حساسیت به مسئله | وضوح گفتار</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>کابینت‌سازان و نجاران کارگاهی | هنرمندان صنایع دستی | برشکاران و پیرایشگران دستی | قلم‌زنان و حکاکان | پرداخت‌کاران و رویه‌کوبان مبلمان | تراشکاران و صیقل‌دهندگان سنگ‌های قیمتی و الماس | دمندگان، قالب‌گیران، خمش‌کاران و پرداخت‌کاران شیشه | پرداخت‌کاران و صیقل‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، پرداخت و پولیش فلز و پلاستیک | خط‌کشان و الگوبرداران فلز و پلاستیک | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران (به‌جز فلز و پلاستیک) | کارگران رنگ‌آمیزی، پوشش‌دهی و تزیین | مدل‌سازان و الگوسازان فلز و پلاستیک | مدل‌سازان و الگوسازان چوب | دوزندگان دستی | سازندگان و تعمیرکاران کفش و مصنوعات چرمی | برشکاران و سنگ‌تراشان سنگ‌های تزیینی و ساختمانی | سازندگان و مونتاژکاران اسکلت‌های فلزی | سنگ‌زن‌ها، سوهان‌کاران و تیزکنندگان ابزار | قالب‌سازان و ابزارسازان صنعتی</t>
+          <t>کابینت‌سازان و نجاران کارگاهی | هنرمندان صنایع دستی | برشکاران و پیرایشگران دستی | حکاکان و اسیدکاران | پرداخت‌کاران و رنگ‌کاران چوب و مبلمان | تراشکاران و صیقل‌دهندگان سنگ‌های قیمتی و الماس | دمندگان، قالب‌گیران، خم‌کاران و پرداخت‌کاران شیشه | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | خط‌کش‌ها و نشانه‌گذاران قطعات فلزی و پلاستیکی | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | الگوسازان فلز و پلاستیک | الگوسازان چوب | دوزندگان دستی | کارگران و تعمیرکاران کفش و چرم | سنگ‌تراشان و حکاکان صنعتی سنگ | سازندگان و مونتاژکاران سازه‌های فلزی | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | قالب‌سازان و ابزارسازان صنعتی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -902,22 +902,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>نرم‌افزار تخصصی طراحی گوهر GemCad | نرم‌افزار طراحی طلا و جواهر | نرم‌افزار پایگاه داده تشخیص و شناسایی سنگ‌های قیمتی | نرم‌افزار ردیابی موجودی | نرم‌افزار تجزیه و تحلیل اسپکتروفتومتر | نرم‌افزار مرورگر وب | نرم‌افزار حسابداری بازرگانی</t>
+          <t>نرم‌افزار تخصصی طراحی گوهر GemCad | نرم‌افزار طراحی طلا و جواهر | نرم‌افزار پایگاه داده تشخیص و شناسایی سنگ‌های قیمتی | نرم‌افزار ردیابی موجودی | نرم‌افزار تجزیه و تحلیل اسپکتروفتومتر | نرم‌افزار مرورگر وب | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | نظارت | تفکر انتقادی</t>
+          <t>گوش دادن فعال | سخن گفتن | نظارت | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | تولید و پردازش | زبان انگلیسی | ریاضیات</t>
+          <t>خدمات مشتری و شخصی | تولید و فرآوری | زبان انگلیسی | ریاضیات</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>دید نزدیک | چابکی انگشتان | ثبات دست و بازو | تشخیص تمایز رنگ‌ها | حساسیت به مسئله | دقت کنترل حرکتی | چابکی دستی | انعطاف‌پذیری بستن الگو | انعطاف‌پذیری در طبقه‌بندی | استدلال قیاسی | بیان شفاهی | درک شفاهی | وضوح گفتار | تشخیص گفتار | توجه انتخابی | تجسم فضایی | مرتب‌سازی اطلاعات</t>
+          <t>بینایی نزدیک | مهارت انگشتان | ثبات دست و بازو | تشخیص رنگ بصری | حساسیت به مسئله | دقت کنترل | مهارت دستی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | بیان شفاهی | درک شفاهی | وضوح گفتار | تشخیص گفتار | توجه انتخابی | تجسم | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>برشکاران و پیرایشگران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | قلم‌زنان و حکاکان | پرداخت‌کاران و صیقل‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، پرداخت و پولیش فلز و پلاستیک | جواهرسازان و سازندگان مصنوعات فلزی و سنگ‌های قیمتی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تراشکاری فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های فرزکاری و صفحه‌تراشی فلز و پلاستیک | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران (به‌جز فلز و پلاستیک) | تکنسین‌های آزمایشگاه و کارگاه ساخت عینک و اپتیک | کارگران رنگ‌آمیزی، پوشش‌دهی و تزیین | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های آبکاری فلز و پلاستیک | متصدیان استخراج و قواره‌بندی سنگ معدن | اپراتورها و متصدیان ماشین‌آلات کفاشی | سازندگان و تعمیرکاران کفش و مصنوعات چرمی | برشکاران و سنگ‌تراشان سنگ‌های تزیینی و ساختمانی | مونتاژکاران و تنظیم‌کنندگان تجهیزات زمان‌سنجی و ساعت | سنگ‌زن‌ها، سوهان‌کاران و تیزکنندگان ابزار | قالب‌سازان و ابزارسازان صنعتی | تعمیرکاران ساعت‌های مچی و دیواری</t>
+          <t>برشکاران و پیرایشگران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | حکاکان و اسیدکاران | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | جواهرسازان و سازندگان مصنوعات فلزی و سنگ‌های قیمتی | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | تکنسین‌های آزمایشگاه و کارگاه ساخت عینک و قطعات اپتیک | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | تنظیم‌کاران و اپراتورهای دستگاه‌های آبکاری فلز و پلاستیک | سنگ‌شکنان و برش‌کاران سنگ معدن | اپراتورها و متصدیان ماشین‌آلات کفش | کارگران و تعمیرکاران کفش و چرم | سنگ‌تراشان و حکاکان صنعتی سنگ | مونتاژکاران و تنظیم‌کنندگان ادوات زمان‌سنجی | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | قالب‌سازان و ابزارسازان صنعتی | تعمیرکاران ساعت‌های مچی و دیواری</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | یادگیری فعال | سخن گفتن | شنیدن فعال</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | یادگیری فعال | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | طراحی | زبان انگلیسی | پزشکی و دندانپزشکی | تولید و پردازش | آموزش و تدریس | خدمات مشتریان و خدمات فردی | مکانیک | رایانه و الکترونیک</t>
+          <t>مدیریت و اداره | طراحی | زبان انگلیسی | پزشکی و دندان‌پزشکی | تولید و فرآوری | آموزش و پرورش | خدمات مشتری و شخصی | مکانیک | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>چابکی انگشتان | دید نزدیک | ثبات دست و بازو | دقت کنترل حرکتی | تجسم فضایی | مرتب‌سازی اطلاعات | استدلال قیاسی | حساسیت به مسئله | توجه انتخابی | چابکی دستی | درک کتبی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری در طبقه‌بندی | درک شفاهی | سرعت ادراک | انعطاف‌پذیری بستن الگو | استدلال استقرایی | بیان شفاهی | تشخیص تمایز رنگ‌ها</t>
+          <t>مهارت انگشتان | بینایی نزدیک | ثبات دست و بازو | دقت کنترل | تجسم | ترتیب‌دهی اطلاعات | استدلال قیاسی | حساسیت به مسئله | توجه انتخابی | مهارت دستی | درک کتبی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | درک شفاهی | سرعت ادراکی | انعطاف‌پذیری بستار | استدلال استقرایی | بیان شفاهی | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، اتصالات و سیستم‌های هواپیما | کارشناسان و تکنسین‌های کالیبراسیون | دستیاران دندانپزشک | بهداشت‌کاران دهان و دندان | دندانپزشکان عمومی | تکنسین‌های آندوسکوپی | قلم‌زنان و حکاکان | پرداخت‌کاران و رویه‌کوبان مبلمان | پرداخت‌کاران و صیقل‌کاران دستی | تکنسین‌های ساخت پروتز و اعضای مصنوعی پزشکی | تعمیرکاران تجهیزات پزشکی | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران (به‌جز فلز و پلاستیک) | تکنسین‌های آزمایشگاه و کارگاه ساخت عینک و اپتیک | متخصصان ارتودنسی | متخصصان ارتز و پروتز | کارگران رنگ‌آمیزی، پوشش‌دهی و تزیین | متخصصان پروتزهای دندانی | سازندگان و مونتاژکاران اسکلت‌های فلزی | تکنسین‌های اتاق عمل | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری سخت و نرم</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | تکنسین‌ها و کارشناسان فنی کالیبراسیون | دستیاران دندان‌پزشک | بهداشت‌کاران دهان و دندان | دندان‌پزشکان عمومی | تکنسین‌های اندوسکوپی | حکاکان و اسیدکاران | پرداخت‌کاران و رنگ‌کاران چوب و مبلمان | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تکنسین‌های ساخت پروتز و اعضای مصنوعی پزشکی | تعمیرکاران تجهیزات پزشکی | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | تکنسین‌های آزمایشگاه و کارگاه ساخت عینک و قطعات اپتیک | متخصصان ارتودنسی | ارتوپدهای فنی و سازندگان اعضای مصنوعی | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | متخصصان پروتزهای دندانی (پروستودنتیست‌ها) | سازندگان و مونتاژکاران سازه‌های فلزی | تکنسین‌های اتاق عمل | تنظیم‌کاران و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن | نظارت | یادگیری فعال | نگارش</t>
+          <t>گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>تولید و پردازش | خدمات مشتریان و خدمات فردی | زبان انگلیسی | مکانیک | طراحی | آموزش و تدریس | ریاضیات</t>
+          <t>تولید و فرآوری | خدمات مشتری و شخصی | زبان انگلیسی | مکانیک | طراحی | آموزش و پرورش | ریاضیات</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | دید نزدیک | بیان شفاهی | استدلال قیاسی | تجسم فضایی | ثبات دست و بازو | مرتب‌سازی اطلاعات | چابکی انگشتان | وضوح گفتار | تشخیص گفتار | چابکی دستی | استدلال استقرایی | هماهنگی چند اندام | دقت کنترل حرکتی | درک کتبی | ابتکار و اصالت | بیان کتبی | تشخیص تمایز رنگ‌ها | استحکام بالاتنه | توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی | حساسیت شنوایی | ادراک عمق</t>
+          <t>درک شفاهی | حساسیت به مسئله | بینایی نزدیک | بیان شفاهی | استدلال قیاسی | تجسم | ثبات دست و بازو | ترتیب‌دهی اطلاعات | مهارت انگشتان | وضوح گفتار | تشخیص گفتار | مهارت دستی | استدلال استقرایی | هماهنگی چند عضو | دقت کنترل | درک کتبی | اصالت | بیان کتبی | تشخیص رنگ بصری | قدرت تنه | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | حساسیت شنوایی | درک عمق</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، اتصالات و سیستم‌های هواپیما | کارشناسان و تکنسین‌های کالیبراسیون | تکنسین‌های پروتزهای دندانی و لابراتوار دندانسازی | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | مونتاژکاران تجهیزات الکترومکانیکی | تکنسین‌های آندوسکوپی | کارشناسان و تکنسین‌های مهندسی مکانیک | آماده‌سازان و تکنسین‌های استریلیزاسیون تجهیزات پزشکی | تعمیرکاران تجهیزات پزشکی | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران (به‌جز فلز و پلاستیک) | تکنسین‌های آزمایشگاه و کارگاه ساخت عینک و اپتیک | جراحان ارتوپد (به‌جز کودکان) | متخصصان ارتز و پروتز | جراحان کودکان | دوزندگان دستی | اپراتورها و متصدیان ماشین‌آلات کفاشی | سازندگان و تعمیرکاران کفش و مصنوعات چرمی | سازندگان و مونتاژکاران اسکلت‌های فلزی | تکنسین‌های اتاق عمل | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جوشکاری، لحیم‌کاری سخت و نرم</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | تکنسین‌ها و کارشناسان فنی کالیبراسیون | تکنسین‌های پروتزهای دندانی و لابراتوار دندانسازی | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | مونتاژکاران تجهیزات الکترومکانیکی | تکنسین‌های اندوسکوپی | کارشناسان و تکنسین‌های مهندسی مکانیک | متصدیان آماده‌سازی و استریل تجهیزات پزشکی | تعمیرکاران تجهیزات پزشکی | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | تکنسین‌های آزمایشگاه و کارگاه ساخت عینک و قطعات اپتیک | جراحان ارتوپدی، غیر از اطفال | ارتوپدهای فنی و سازندگان اعضای مصنوعی | جراحان اطفال | دوزندگان دستی | اپراتورها و متصدیان ماشین‌آلات کفش | کارگران و تعمیرکاران کفش و چرم | سازندگان و مونتاژکاران سازه‌های فلزی | تکنسین‌های اتاق عمل | تنظیم‌کاران و اپراتورهای دستگاه‌های جوشکاری و لحیم‌کاری</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
